--- a/decks/infinity-vans/keyword-research.xlsx
+++ b/decks/infinity-vans/keyword-research.xlsx
@@ -76,11 +76,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
@@ -92,6 +87,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -128,11 +128,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -568,12 +568,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diesel Heater for Van: What Actually Works in a Van</t>
+          <t>Thinsulate Insulation for Vans: Is It Worth the Premium?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>diesel heater for van</t>
+          <t>thinsulate insulation</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -606,12 +606,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sprinter Heater: Sized and Specced for Real Builds</t>
+          <t>12V Air Conditioners for Vans: Real Cooling Without Shore Power</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sprinter heater</t>
+          <t>12v air conditioner for van</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -626,14 +626,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -644,12 +644,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sprinter Battery: How to Get It Right the First Time</t>
+          <t>Installing a Sprinter Van Heater: A Step-by-Step Walkthrough</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sprinter battery</t>
+          <t>sprinter van heater</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
         <v>210</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -682,12 +682,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mercedes Benz Sprinter Battery: A No-Nonsense Buyer's Guide</t>
+          <t>Camper Van Batteries: How Much Power Your Build Actually Needs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mercedes benz sprinter battery</t>
+          <t>van battery</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -720,12 +720,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camper Van Water Tank: The Questions to Ask Before You Buy</t>
+          <t>The MaxxAir Deluxe Fan: Why Ventilation Is a Van's Best Upgrade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>camper van water tank</t>
+          <t>maxxair deluxe fan</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -740,14 +740,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -758,12 +758,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Van Roof Fan: A Practical Spec for Your Build</t>
+          <t>Designing a Van Ventilation System: Fans, Vents, and Airflow</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>van roof fan</t>
+          <t>van ventilation system</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -778,11 +778,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>2</v>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12V Aircon for Van: A No-Nonsense Buyer's Guide</t>
+          <t>Van Heating Systems: Choosing Between Diesel, Propane, and Electric</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12v aircon for van</t>
+          <t>van heating system</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -834,7 +834,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Van Insulation: What Actually Works (and What’s a Waste of Money)</t>
+          <t>Van Insulation: What Actually Works (and What's a Waste of Money)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Best Insulation for Camper: What's Worth the Money</t>
+          <t>The Best-Insulated Campers, and How to Match Them in Your Build</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>best insulation for camper</t>
+          <t>best insulated campers</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -910,12 +910,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Electric Camper Vans: A Step-by-Step Primer</t>
+          <t>The Best Insulation for a Camper: A Material-by-Material Guide</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>electric camper vans</t>
+          <t>best insulation for camper</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -925,19 +925,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>390</v>
+        <v>90</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -948,7 +948,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Van Conversion Kits: What to Look for in a Quality Flat-Pack Build</t>
+          <t>Van Conversion Kits: What to Look For in a Quality Flat-Pack Build</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>2</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Camper Van with Bathroom: How to Choose the Right One for Your Van</t>
+          <t>Camper Vans with a Bathroom: Fitting a Wet Bath That Works</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Van Air Con: What Serious DIY Builders Choose</t>
+          <t>Van Showers: Indoor, Outdoor, and DIY Options That Work</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>van air con</t>
+          <t>van shower</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1082,14 +1082,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>880</v>
+        <v>480</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ram ProMaster Conversion Kits: The Components That Actually Matter</t>
+          <t>Camper Van Conversion Kits: A DIY Builder's Buying Guide</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ram promaster conversion kit</t>
+          <t>camper van conversion kit</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
+        <v>320</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="17">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Converted Van: A No-Compromise Build, Faster</t>
+          <t>Camper Van Conversion: A First-Timer's Van-to-Home Roadmap</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>converted van</t>
+          <t>camper van conversion</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Best Camper Vans: How the Top Options Compare</t>
+          <t>The Best Camper Vans of 2026, Compared by Build and Budget</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Best Rated Camper Vans: How to Pick the Right System</t>
+          <t>The Cheapest Way to Build a Campervan in 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>best rated camper vans</t>
+          <t>cheapest campervans</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Best Work Van: The Real Numbers Behind the Build</t>
+          <t>Van Size Comparison Chart: Sprinter vs Transit vs ProMaster</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>best work van</t>
+          <t>van size comparison chart</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>480</v>
+        <v>110</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maybach Van: Explained in Plain English</t>
+          <t>2-Berth Campervans: The Best Layouts for Two Travelers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>maybach van</t>
+          <t>2 berth campervan</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2900</v>
+        <v>880</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cheapest Camper Van: A 2026 Buyer's Guide</t>
+          <t>Air Conditioner in a Van: Rooftop, Under-Bed, and 12V Options</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cheapest camper van</t>
+          <t>air conditioner in van</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1343,19 +1343,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>320</v>
+        <v>590</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Conversion Van: A Clear Explainer for First-Time Builders</t>
+          <t>Building an Adventure Van: Gear, Layout, and Go-Anywhere Setup</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>conversion van</t>
+          <t>adventure van</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>18100</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>37</v>
+        <v>1300</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -1404,15 +1404,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Van Life Toilet: A Plan You Can Actually Build</t>
+          <t>Portable Power Stations for Van Life: Plug-and-Play vs Wired</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>van life toilet</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+          <t>portable power station for van life</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -1442,15 +1442,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Van Life Sprinter: The Questions to Ask Before You Buy</t>
+          <t>Vanlife Bedding: Staying Warm and Organized in a Small Bed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>van life sprinter</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+          <t>vanlife bedding</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1480,15 +1480,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Van Life Conversions: A Realistic Build Roadmap</t>
+          <t>Van Life Vans: Choosing the Right Platform for the Road</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>van life conversions</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+          <t>van life vans</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>47</v>
+        <v>480</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -1518,15 +1518,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Best Van Life Vans: How to Plan It Without Regrets</t>
+          <t>The Best Power Stations for Van Life, by Real Capacity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>best van life vans</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+          <t>best power stations for van life</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>480</v>
+        <v>70</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -1556,15 +1556,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DIY Overland Trailer: What Every New Builder Should Know</t>
+          <t>DIY Camper Van: How to Build One Without Losing Your Mind</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>diy overland trailer</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+          <t>diy camper van</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -1583,7 +1583,7 @@
         <v>480</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1594,34 +1594,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Best Power Station for Van Life: The Trade-offs Worth Knowing</t>
+          <t>Mercedes Sprinter Van Life: Why It's the Default, and the Trade-offs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>best power station for van life</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+          <t>mercedes sprinter van life</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1632,15 +1632,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Best Mattress for Van Life: The Real Numbers Behind the Build</t>
+          <t>The Best Vehicle for Van Life: Van, SUV, or Something Bigger?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>best mattress for van life</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
+          <t>best vehicle for van life</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1670,22 +1670,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>How to Convert a Van Into a Camper: A Realistic Build Roadmap</t>
+          <t>Is Van Life Worth It? An Honest Look at the Trade-offs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>how to convert a van into a camper</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
+          <t>is van life worth it</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>42</v>
+        <v>140</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -1708,34 +1708,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luxury Sprinter Van: Specs That Actually Matter for a Build</t>
+          <t>How Much Does It Cost to Convert a Van? The Real 2026 Numbers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>luxury sprinter van</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Platforms &amp; Buying</t>
+          <t>how much does it cost to convert a van</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>17</v>
+        <v>880</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="33">
@@ -1746,15 +1746,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Builder's Guide to Ford Transit Seats</t>
+          <t>Ford Transit Connect Camper: How Far a Mini-Van Build Can Go</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ford transit seats</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
+          <t>ford transit connect camper</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>720</v>
+        <v>1600</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -1784,15 +1784,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sprinter Travel Van: Which Platform Fits Your Build</t>
+          <t>Sprinter Reclining Seats: A 4-Seater Setup That Sleeps Two</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sprinter travel van</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
+          <t>sprinter reclining seats 4 seater</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1822,15 +1822,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camper Mercedes Benz Sprinter: Which Platform Fits Your Build</t>
+          <t>Ford Transit Medium Roof: Can You Build in It, or Go High?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>camper mercedes benz sprinter</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
+          <t>ford transit medium roof</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>36</v>
+        <v>720</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -1860,15 +1860,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ford Transit AWD: A No-Nonsense Buyer's Guide</t>
+          <t>Ford Transit Roof Racks: Mounting Gear, Solar, and More</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ford transit awd</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
+          <t>ford transit racks</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>41</v>
+        <v>390</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Transit vs Sprinter: Which Van Should You Actually Build In?</t>
+          <t>Transit vs Sprinter: Which Should You Actually Build In?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1906,7 +1906,7 @@
           <t>transit vs sprinter</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Transit Cargo Van: What Every Converter Should Know</t>
+          <t>The Ford Transit Cargo Van: The Best Blank Canvas for a Build?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1944,7 +1944,7 @@
           <t>ford transit cargo van</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -1974,15 +1974,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mercedes Sprinter Cost: Head to Head, for Camper Builds</t>
+          <t>Ford Transit vs Mercedes Sprinter: The Full Spec Breakdown</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mercedes sprinter cost</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
+          <t>ford transit vs mercedes sprinter</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2012,15 +2012,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Benz Van Price, Compared</t>
+          <t>The Best Van for Camping: Weekend-Ready vs Full-Time Builds</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>benz van price</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
+          <t>best van for camping</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -2032,11 +2032,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>9</v>
@@ -2050,34 +2050,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camping Car Van Mercedes, Explained</t>
+          <t>The Best Van to Convert in 2026: A Platform Buyer's Guide</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>camping car van mercedes</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
+          <t>best van</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8100</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>32</v>
+        <v>1000</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="42">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thinsulate Insulation: A Practical Spec for Your Build</t>
+          <t>Campervan Solar Power: Sizing a System for Off-Grid Living</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>thinsulate insulation</t>
+          <t>campervan solar power</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>880</v>
+        <v>210</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12V Air Conditioner for Van: What Actually Works in a Van</t>
+          <t>Mercedes-Benz Sprinter Battery Setup: Starter, Leisure, and Lithium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12v air conditioner for van</t>
+          <t>mercedes benz sprinter battery</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2146,14 +2146,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sprinter Van Heater: Sized and Specced for Real Builds</t>
+          <t>Designing a Van Solar System: From One Panel to Full Off-Grid</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sprinter van heater</t>
+          <t>van solar system</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Builder's Guide to Overlanding Fridge</t>
+          <t>Van Roof Fans: The Cheapest Comfort Upgrade You'll Ever Make</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>overlanding fridge</t>
+          <t>van roof fan</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Everything You Need in Camper Van Insulation</t>
+          <t>Building a Campervan Water System: Tanks, Pumps, and Plumbing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>camper van insulation</t>
+          <t>campervan water system</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Van Roof Ventilation: How to Get It Right the First Time</t>
+          <t>Campervan Electrical Systems, Explained for First-Time Builders</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>van roof ventilation</t>
+          <t>campervan electrical system</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2293,19 +2293,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Campervan Electrical Systems, Explained for First-Time Builders</t>
+          <t>Building a Solar-Powered Van: Panels, Batteries, and Real Output</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>campervan electrical system</t>
+          <t>solar powered van</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>90</v>
+        <v>390</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Best Van Insulation: Cost, Performance, and Trade-offs</t>
+          <t>Cargo Van Insulation: Beating Condensation Before It Starts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>best van insulation</t>
+          <t>cargo van insulation</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2369,16 +2369,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>4</v>
@@ -2392,34 +2392,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Van Water Tank: A Clear Explainer for Builders</t>
+          <t>Sprinter Van Conversion Kits: From Empty Cargo Van to Camper</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>van water tank</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Systems &amp; Insulation</t>
+          <t>sprinter van conversion kit</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Kits &amp; Components</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -2430,34 +2430,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What Is Cargo Van Insulation? A Builder's Primer</t>
+          <t>Van Galley Kits: A Camper Kitchen You Can Install in a Weekend</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>cargo van insulation</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Systems &amp; Insulation</t>
+          <t>van galley kit</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Kits &amp; Components</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sprinter Van Conversion Kits: From Cargo Van to Camper in a Weekend</t>
+          <t>Small Camper Vans: Big Comfort in a Compact, Drivable Build</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sprinter van conversion kit</t>
+          <t>small camper vans</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>260</v>
+        <v>1900</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Van Galley Kits: Building a Camper Kitchen That Actually Works</t>
+          <t>Camper Van Interior Ideas: Layouts That Live Big in Small Space</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>van galley kit</t>
+          <t>camper van interior</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>170</v>
+        <v>880</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Small Camper Vans: What's Included, and What Isn't</t>
+          <t>Ram ProMaster Conversion Kits: The Parts That Actually Matter</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>small camper vans</t>
+          <t>ram promaster conversion kit</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1900</v>
+        <v>70</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Van Ac Unit: From Cargo Van to Camper in a Weekend</t>
+          <t>Flat-Pack Van Conversion vs Full Custom: Cost, Time, and Fit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>van ac unit</t>
+          <t>flat pack van conversion</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>720</v>
+        <v>210</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Conversion Vans: What to Look for in a Quality Kit</t>
+          <t>Low-Cost Camper Van Builds: Where to Save and Where Not To</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>conversion vans</t>
+          <t>camper van low cost</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2635,19 +2635,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>56</v>
+        <v>880</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Flat-Pack Van Conversion: Cost, Install Time, and Fitment</t>
+          <t>The Best Gas-Mileage Vans for Conversion, by Real MPG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>flat pack van conversion</t>
+          <t>best gas mileage van</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Camper Van Low Cost: Flat-Pack vs Full Custom</t>
+          <t>The Best Conversion Vans in 2026, Ranked for DIY Builders</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>camper van low cost</t>
+          <t>best conversion van</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2716,11 +2716,11 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>880</v>
+        <v>140</v>
       </c>
       <c r="H58" s="4" t="n">
         <v>15</v>
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Travel Van: What Every DIY Builder Should Know</t>
+          <t>The Best Off-Road Vans for Building an Overland Rig</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>travel van</t>
+          <t>best off road van</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2749,19 +2749,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>4400</v>
+        <v>90</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hippie Van: A Beginner's Primer</t>
+          <t>Camper Van News: The 2026 Trends Builders Are Watching</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hippie van</t>
+          <t>camper van news</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>3600</v>
+        <v>720</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Best Gas Mileage Van: Where Most Builders Get It Wrong</t>
+          <t>Van Conversion 101: How a Cargo Van Becomes a Camper</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>best gas mileage van</t>
+          <t>van conversion</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>17</v>
+        <v>2400</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="62">
@@ -2848,22 +2848,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Best Campervan Conversions: Cost, Install Time, and Fitment</t>
+          <t>Sprinter Camper Layouts: Making the Most of 144 and 170</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>best campervan conversions</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Kits &amp; Components</t>
+          <t>sprinter camper layout</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>260</v>
+        <v>50</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -2886,34 +2886,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Van As Camper: The Fundamentals, Minus the Jargon</t>
+          <t>The Best Van Life Mattress: Comfort That Fits Your Bed Platform</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>van as camper</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Kits &amp; Components</t>
+          <t>van life mattress</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>18100</v>
-      </c>
-      <c r="H63" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2924,15 +2924,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Van DIY Camper: A Realistic Build Roadmap</t>
+          <t>Van Life Showers: Staying Clean on the Road, Indoors or Out</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>van diy camper</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
+          <t>van life shower</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2962,22 +2962,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vans for Van Life: From Empty Van to Finished Camper</t>
+          <t>The Best Vans for Van Life in 2026, Ranked by Build Cost</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vans for van life</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
+          <t>best vans for van life</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>110</v>
+        <v>880</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Builder's Guide to Sprinter Camper Layout</t>
+          <t>DIY Overland Trailers: A Towable Alternative to a Full Build</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sprinter camper layout</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
+          <t>diy overland trailer</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>50</v>
+        <v>480</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -3038,34 +3038,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Van Life Vans: A Plan You Can Actually Build</t>
+          <t>DIY Van Conversions: A Stage-by-Stage Guide for Beginners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>van life vans</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
+          <t>diy van conversions</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="H67" s="7" t="n">
-        <v>42</v>
+      <c r="H67" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="68">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Van Life Shower: A Plan You Can Actually Build</t>
+          <t>Converting a Van to a High Top: Is the Roof Raise Worth It?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>van life shower</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
+          <t>convert van to high top</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
@@ -3114,15 +3114,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Best Vans for Van Life: What It Really Costs and Takes</t>
+          <t>The Best Batteries for Van Life: Lithium vs AGM, Sized Right</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>best vans for van life</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
+          <t>best batteries for van life</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>880</v>
+        <v>30</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3152,34 +3152,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Van Life Essentials: A Clear Guide for First-Timers</t>
+          <t>DIY Van Builds: What to Tackle Yourself and What to Outsource</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>van life essentials</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
+          <t>diy van</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>11</v>
+        <v>480</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="71">
@@ -3190,22 +3190,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Best Vanlife Vans: What It Really Costs and Takes</t>
+          <t>Ram Camper Van: Building on the Budget-Friendly ProMaster</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>best vanlife vans</t>
+          <t>ram camper van</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Van Life &amp; Planning</t>
+          <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>90</v>
+        <v>1300</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
@@ -3228,34 +3228,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Best Van for Vanlife: What to Know Before You Commit</t>
+          <t>The Mercedes 2500 Van: Picking the Right Sprinter for a Build</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>best van for vanlife</t>
+          <t>mercedes 2500 van</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Van Life &amp; Planning</t>
+          <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>40</v>
+        <v>590</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
@@ -3266,34 +3266,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>How Much Does It Cost to Convert a Van? The Real Numbers</t>
+          <t>Dodge Ram Camper Van: Is the ProMaster the Value Pick?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>how much does it cost to convert a van</t>
+          <t>dodge ram camper van</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Van Life &amp; Planning</t>
+          <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="H73" s="7" t="n">
-        <v>38</v>
+      <c r="H73" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -3304,15 +3304,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ford Transit Connect Camper: The Right Van for How You'll Use It</t>
+          <t>Ford Transit Shelving: Modular Storage for Work and Camper Builds</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ford transit connect camper</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
+          <t>ford transit shelving</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1600</v>
+        <v>480</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -3342,15 +3342,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sprinter Reclining Seats 4 Seater: What to Know Before You Buy</t>
+          <t>The Dually Sprinter Van: When Six Wheels Actually Make Sense</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sprinter reclining seats 4 seater</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
+          <t>dually sprinter van</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -3362,14 +3362,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>720</v>
+        <v>260</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76">
@@ -3380,15 +3380,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dodge Ram Camper Van: What to Look for Before You Buy</t>
+          <t>Ford Transit Camper Van: America's Best-Selling Conversion Base</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dodge ram camper van</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr">
+          <t>transit camper van</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -3406,8 +3406,8 @@
       <c r="G76" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="H76" s="4" t="n">
-        <v>15</v>
+      <c r="H76" s="6" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="77">
@@ -3418,22 +3418,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sprinter Camper Van: What to Look for Before You Buy</t>
+          <t>The Best Van for a Camper Conversion: A Side-by-Side Pick</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sprinter camper van</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
+          <t>best van for camper conversion</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>5400</v>
-      </c>
-      <c r="H77" s="7" t="n">
-        <v>33</v>
+        <v>480</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -3456,34 +3456,34 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Best Vans for a Camper Conversion, Compared</t>
+          <t>Turning a Sprinter Van Into a Camper: Where to Begin</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>best van for camper conversion</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
+          <t>sprinter van camper</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>480</v>
+        <v>5400</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79">
@@ -3494,15 +3494,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mercedes Benz Sprinter Van Price: Cost, Reliability, and Resale</t>
+          <t>The Best Sprinter Van for a Camper Conversion, by Trim</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>mercedes benz sprinter van price</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
+          <t>best sprinter van</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>590</v>
+        <v>260</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
@@ -3532,15 +3532,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Transit vs Mercedes Sprinter: What It Costs to Own and Run</t>
+          <t>The Best Years for a Used Ford Transit Build</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ford transit vs mercedes sprinter</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
+          <t>best years for ford transit</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>390</v>
+        <v>90</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -3570,15 +3570,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Best Van: The Real Trade-offs for Converters</t>
+          <t>The Best Vans for Road Trips: Comfort, Range, and Reliability</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>best van</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
+          <t>best van for road trips</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H81" s="7" t="n">
-        <v>44</v>
+        <v>110</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Overland Fridge: How to Get It Right the First Time</t>
+          <t>Diesel Heaters for Vans: What Actually Works, and What's Overkill</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>overland fridge</t>
+          <t>diesel heater for van</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>590</v>
+        <v>1000</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Campervan Solar Power: A Practical Spec for Your Build</t>
+          <t>How to Choose an Overland Fridge: Size, Power Draw, and Top Picks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>campervan solar power</t>
+          <t>overland fridge</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>210</v>
+        <v>590</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mercedes Sprinter Battery: What Separates Good From Cheap</t>
+          <t>Heating a Sprinter Van: Diesel vs Electric, and What Keeps You Warm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mercedes sprinter battery</t>
+          <t>sprinter heater</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Van Solar System: What to Know Before You Buy</t>
+          <t>Sprinter Battery Banks: Wiring, Capacity, and Charging on the Road</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>van solar system</t>
+          <t>sprinter battery</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Maxxair Deluxe Fan: What Actually Works in a Van</t>
+          <t>Overlanding Fridges: Dual-Zone Cooling, Power Use, and Mounting</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>maxxair deluxe fan</t>
+          <t>overlanding fridge</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Van Ventilation System: Sized and Specced for Real Builds</t>
+          <t>Van Roof Ventilation: Stopping Moisture, Heat, and Stale Air</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>van ventilation system</t>
+          <t>van roof ventilation</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3818,14 +3818,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Van Heaters: What Separates Good From Cheap</t>
+          <t>Van Sound Insulation: Quieting Road Noise Without Adding Bulk</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>van heaters</t>
+          <t>van sound insulation</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Best Insulated Campers: How the Options Compare</t>
+          <t>Van Ventilation 101: Why Airflow Makes or Breaks a Build</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>best insulated campers</t>
+          <t>van ventilation</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3898,10 +3898,10 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Solar Powered Van: What Every Van Build Should Know</t>
+          <t>The Best Van Insulation in 2026, Ranked by Real Performance</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>solar powered van</t>
+          <t>best van insulation</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3927,19 +3927,19 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Campervan Insulation: A Clear Explainer for Builders</t>
+          <t>Camper Van Water Tanks: Sizing, Placement, and How Much You Need</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>campervan insulation</t>
+          <t>van water tank</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -3988,34 +3988,34 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ford Transit Conversion Kits: What’s Included, and What Isn’t</t>
+          <t>Electric Camper Vans: Are EV Conversions Ready for Van Life?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ford transit conversion kit</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Kits &amp; Components</t>
+          <t>electric camper vans</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Systems &amp; Insulation</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
@@ -4026,34 +4026,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>All Wheel Drive Van: A Buyer's Guide for DIY Builders</t>
+          <t>Campervan Insulation Explained: Materials, R-Value, and Method</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>all wheel drive van</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Kits &amp; Components</t>
+          <t>campervan insulation</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Systems &amp; Insulation</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2400</v>
+        <v>210</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Luxury Van: Flat-Pack vs Custom, Weighed Honestly</t>
+          <t>Ford Transit Conversion Kits: What's Included and What's Not</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>luxury van</t>
+          <t>ford transit conversion kit</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>1900</v>
+        <v>320</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Camper Van Conversion Kits: A Buyer’s Guide for DIY Builders</t>
+          <t>All-Wheel-Drive Vans: Do You Really Need AWD for Van Life?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>camper van conversion kit</t>
+          <t>all wheel drive van</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H95" s="7" t="n">
-        <v>30</v>
+        <v>2400</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="96">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Car on Van: Sized, Priced, and Ready to Install</t>
+          <t>Van Air Con: Keeping a Camper Cool On-Grid and Off</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>car on van</t>
+          <t>van air con</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H96" s="6" t="n">
-        <v>64</v>
+        <v>880</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Best Small Camper Vans: Cost, Install Time, and Fitment</t>
+          <t>Camper Van Kitchen Ideas: Galley Layouts and What to Skip</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>best small camper vans</t>
+          <t>van kitchen</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>49500</v>
+        <v>590</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Best Camper Van: What It Really Costs in 2026</t>
+          <t>What a Converted Van Includes: Anatomy of a Finished Build</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>best camper van</t>
+          <t>converted van</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>880</v>
-      </c>
-      <c r="H98" s="4" t="n">
-        <v>13</v>
+        <v>1900</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="99">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Best Travel Van: The Trade-offs No One Mentions</t>
+          <t>The Best Small Camper Vans in 2026 (and How to Build Your Own)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>best travel van</t>
+          <t>best small camper vans</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>590</v>
+        <v>49500</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cheapest Campervans: What to Know Before You Commit</t>
+          <t>The Best-Rated Camper Vans, and What Earns the Rating</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>cheapest campervans</t>
+          <t>best rated camper vans</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>25' Van Chassis Length: A Quick, Honest Overview</t>
+          <t>The Best High-Mileage Vans to Convert (and Keep for Years)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>25' van chassis length</t>
+          <t>best mileage van</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -4345,19 +4345,19 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>1900</v>
+        <v>210</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Best Conversion Vans: How the Top Options Compare</t>
+          <t>4WD Vans for Off-Grid Travel: When the Upgrade Is Worth It</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>best conversion vans</t>
+          <t>4wd van</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -4383,16 +4383,16 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="H102" s="4" t="n">
         <v>16</v>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Van a Car: What You Should Know First</t>
+          <t>High-Top Vans: Why Roof Height Makes or Breaks a Conversion</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>van a car</t>
+          <t>high top van</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>2900</v>
-      </c>
-      <c r="H103" s="6" t="n">
-        <v>53</v>
+        <v>480</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="104">
@@ -4444,22 +4444,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Van Life Accessories: From Empty Van to Finished Camper</t>
+          <t>Van Storage Ideas: Smart Solutions for Every Inch of Space</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>van life accessories</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t>Van Life &amp; Planning</t>
+          <t>van storage ideas</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Kits &amp; Components</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
@@ -4482,22 +4482,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Van Life Toilet Options: What to Know Before You Buy</t>
+          <t>What a Camper Van Really Costs: Van, Kit, and Build Budget</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>van life toilet options</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>Van Life &amp; Planning</t>
+          <t>van cost</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Kits &amp; Components</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H105" s="4" t="n">
-        <v>8</v>
+        <v>260</v>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="106">
@@ -4520,15 +4520,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Vanlife Van: From Empty Van to Finished Camper</t>
+          <t>Van Life Toilets: Composting, Cassette, and What to Actually Buy</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>vanlife van</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
+          <t>van life toilet</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="H106" s="7" t="n">
-        <v>46</v>
+        <v>140</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -4558,15 +4558,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vanlife Shower: A Realistic Build Roadmap</t>
+          <t>Van Life Toilet Options Compared: Cost, Cleanup, and Smell</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>vanlife shower</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr">
+          <t>van life toilet options</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -4596,34 +4596,34 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>How to Plan Your Van Build Before You Buy a Single Part</t>
+          <t>The Best Van Life Parking Apps for Finding a Safe Spot</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>van build planning</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
+          <t>van life parking app</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -4634,34 +4634,34 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Best Power Stations for Van Life: The Trade-offs Worth Knowing</t>
+          <t>How to Plan Your Van Build Before You Buy a Single Part</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>best power stations for van life</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
+          <t>van build planning</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110">
@@ -4672,34 +4672,34 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Best Van Life Accessories: How to Plan It Without Regrets</t>
+          <t>Van Life Essentials: The Gear That Actually Earns Its Space</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>best van life accessories</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
+          <t>van life essentials</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>50</v>
+        <v>590</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111">
@@ -4710,15 +4710,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DIY Camper Van: Where to Start, Step by Step</t>
+          <t>Camper Van Layouts: The Floor Plans That Actually Live Well</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>diy camper van</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
+          <t>camper van layout</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>480</v>
+        <v>260</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
@@ -4748,34 +4748,34 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ram Camper Van: What Separates Good From Cheap</t>
+          <t>How to Convert a Van Into a Camper: A Realistic Build Roadmap</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ram camper van</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>Platforms &amp; Buying</t>
+          <t>how to convert a van into a camper</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H112" s="4" t="n">
-        <v>11</v>
+        <v>1600</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="113">
@@ -4786,34 +4786,34 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mercedes 2500 Van: The Questions to Ask Before You Buy</t>
+          <t>The Van Life Collective: Finding Your Community on the Road</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>mercedes 2500 van</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Platforms &amp; Buying</t>
+          <t>van life collective</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Van Life &amp; Planning</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>590</v>
-      </c>
-      <c r="H113" s="4" t="n">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="114">
@@ -4824,15 +4824,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Everything You Need in Sprinter Seats</t>
+          <t>Ford Transit Seats: Swivels, Benches, and Bed-Ready Setups</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>sprinter seats</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
+          <t>ford transit seats</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -4851,7 +4851,7 @@
         <v>720</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -4862,15 +4862,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AWD Van: A Buyer's Guide for Converters</t>
+          <t>Ford Transit Van Engines: EcoBoost, Diesel, and What Lasts</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>awd van</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
+          <t>ford transit van engine</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>4400</v>
-      </c>
-      <c r="H115" s="7" t="n">
-        <v>32</v>
+        <v>320</v>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="116">
@@ -4900,22 +4900,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>The Most Reliable Vans to Convert, by the Real Data</t>
+          <t>Ford Transit Accessories Worth Adding Before Your Build</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>most reliable van</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
+          <t>ford transit accessories</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>480</v>
+        <v>590</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4938,34 +4938,34 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mercedes Camper Van: The Short Version for Busy Builders</t>
+          <t>The Most Reliable Vans to Convert, by the Real Data</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>mercedes camper van</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
+          <t>most reliable van</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>9900</v>
+        <v>480</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118">
@@ -4976,34 +4976,34 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Best MPG Van: Which One Should You Build In</t>
+          <t>Mercedes Camper Vans: Why the Sprinter Still Sets the Standard</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>best mpg van</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
+          <t>mercedes camper van</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>480</v>
+        <v>9900</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119">
@@ -5014,15 +5014,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>The Beginner's Guide to Sprinter Van Camper</t>
+          <t>The Mercedes Sprinter Camper Van: Specs That Matter for a Build</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>sprinter van camper</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
+          <t>mercedes sprinter camper van</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120">
@@ -5052,34 +5052,34 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Automatic Sprinter Van: A Clear Explainer for First-Time Buyers</t>
+          <t>Ford Transit Model Comparison: Wheelbase, Roof, and Engine</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>automatic sprinter van</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
+          <t>ford transit model comparison</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>33100</v>
-      </c>
-      <c r="H120" s="7" t="n">
-        <v>32</v>
+        <v>90</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="121">
@@ -5090,34 +5090,34 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Is Mercedes Sprinter Van Cost Worth It?</t>
+          <t>The Automatic Sprinter Van: What Builders Should Know About It</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>mercedes sprinter van cost</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
+          <t>automatic sprinter van</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>720</v>
-      </c>
-      <c r="H121" s="7" t="n">
-        <v>33</v>
+        <v>33100</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5219,7 +5219,7 @@
           <t>automatic sprinter van</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5237,7 +5237,7 @@
       <c r="E3" s="3" t="n">
         <v>33100</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -5270,7 +5270,7 @@
       <c r="E4" s="3" t="n">
         <v>22200</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -5285,7 +5285,7 @@
           <t>ford transit cargo van</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5336,12 +5336,12 @@
       <c r="E6" s="3" t="n">
         <v>18100</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       <c r="E7" s="3" t="n">
         <v>18100</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
           <t>sprinter van sprinter van</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5402,7 +5402,7 @@
       <c r="E8" s="3" t="n">
         <v>14800</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -5417,7 +5417,7 @@
           <t>mercedes camper van</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5450,7 +5450,7 @@
           <t>camper mercedes benz sprinter</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5468,12 +5468,12 @@
       <c r="E10" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
           <t>camping car van mercedes</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5501,12 +5501,12 @@
       <c r="E11" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
           <t>sprinter van camper</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5549,7 +5549,7 @@
           <t>sprinter camper van</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5567,12 +5567,12 @@
       <c r="E13" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
           <t>transit van van</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5600,7 +5600,7 @@
       <c r="E14" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -5615,7 +5615,7 @@
           <t>mercedes sprinter camper van</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5636,9 +5636,9 @@
       <c r="F15" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
           <t>awd van</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5666,12 +5666,12 @@
       <c r="E16" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       <c r="E17" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5735,9 +5735,9 @@
       <c r="F18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
           <t>mbz sprinter camper</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5780,7 +5780,7 @@
           <t>ford sprinter van</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5798,7 +5798,7 @@
       <c r="E20" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>61</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -5834,9 +5834,9 @@
       <c r="F21" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
           <t>mercedes van camper</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5864,7 +5864,7 @@
       <c r="E22" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -5879,7 +5879,7 @@
           <t>mercedes sprinter 2500</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5930,12 +5930,12 @@
       <c r="E24" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
           <t>ford transit trail</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -5996,12 +5996,12 @@
       <c r="E26" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
           <t>benz sprinter camper</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6029,7 +6029,7 @@
       <c r="E27" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -6044,7 +6044,7 @@
           <t>ford transit awd</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6062,12 +6062,12 @@
       <c r="E28" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6098,9 +6098,9 @@
       <c r="F29" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
           <t>mercedes sprinter van camper</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6128,7 +6128,7 @@
       <c r="E30" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -6143,7 +6143,7 @@
           <t>luxury sprinter van</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6164,9 +6164,9 @@
       <c r="F31" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
           <t>ford transit camper van</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6209,7 +6209,7 @@
           <t>ford transit conversion van</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6242,7 +6242,7 @@
           <t>4x4 van</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6308,7 +6308,7 @@
           <t>ford camper van</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6326,7 +6326,7 @@
       <c r="E36" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -6341,7 +6341,7 @@
           <t>ford van models</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6359,7 +6359,7 @@
       <c r="E37" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -6374,7 +6374,7 @@
           <t>mb sprinter camper</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6407,7 +6407,7 @@
           <t>mercedes benz camper van</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6425,7 +6425,7 @@
       <c r="E39" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -6440,7 +6440,7 @@
           <t>mercedes sprinter 4x4</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6458,7 +6458,7 @@
       <c r="E40" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -6473,7 +6473,7 @@
           <t>mercedes sprinter camping</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6491,7 +6491,7 @@
       <c r="E41" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -6506,7 +6506,7 @@
           <t>mercedes sprinter van interior</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6539,7 +6539,7 @@
           <t>ram promaster van</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6557,7 +6557,7 @@
       <c r="E43" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>55</v>
       </c>
       <c r="G43" t="inlineStr">
@@ -6590,12 +6590,12 @@
       <c r="E44" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
           <t>mercedes passenger van</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6659,9 +6659,9 @@
       <c r="F46" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
           <t>sprinter van conversion</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6689,7 +6689,7 @@
       <c r="E47" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -6737,7 +6737,7 @@
           <t>mb sprinter van 4x4</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6755,7 +6755,7 @@
       <c r="E49" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -6803,7 +6803,7 @@
           <t>ford transit 250 high roof</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6821,7 +6821,7 @@
       <c r="E51" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G51" t="inlineStr">
@@ -6836,7 +6836,7 @@
           <t>ford transit mpg</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6869,7 +6869,7 @@
           <t>maybach sprinter</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -6956,9 +6956,9 @@
       <c r="F55" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G55" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
           <t>bmw sprinter camper</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7019,7 +7019,7 @@
       <c r="E57" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="9" t="n">
         <v>50</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -7034,7 +7034,7 @@
           <t>interior mercedes benz sprinter</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7067,7 +7067,7 @@
           <t>mercedes benz sprinter 4x4</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7085,7 +7085,7 @@
       <c r="E59" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G59" t="inlineStr">
@@ -7100,7 +7100,7 @@
           <t>mercedes sprinter interior</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7133,7 +7133,7 @@
           <t>mercedes sprinter van 4x4</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7166,7 +7166,7 @@
           <t>mercedes transit van</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7217,7 +7217,7 @@
       <c r="E63" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G63" t="inlineStr">
@@ -7232,7 +7232,7 @@
           <t>sprinter van interior</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7265,7 +7265,7 @@
           <t>sprinter passenger van</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7382,7 +7382,7 @@
       <c r="E68" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G68" t="inlineStr">
@@ -7397,7 +7397,7 @@
           <t>dodge sprinter van</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7415,7 +7415,7 @@
       <c r="E69" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F69" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G69" t="inlineStr">
@@ -7430,7 +7430,7 @@
           <t>cargo van ford</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7463,7 +7463,7 @@
           <t>maybach sprinter van</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7547,12 +7547,12 @@
       <c r="E73" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F73" s="7" t="n">
+      <c r="F73" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       <c r="E74" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="9" t="n">
         <v>70</v>
       </c>
       <c r="G74" t="inlineStr">
@@ -7646,7 +7646,7 @@
       <c r="E76" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F76" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G76" t="inlineStr">
@@ -7679,7 +7679,7 @@
       <c r="E77" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F77" s="7" t="n">
+      <c r="F77" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G77" t="inlineStr">
@@ -7694,7 +7694,7 @@
           <t>ford transit camper</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7727,7 +7727,7 @@
           <t>ford transit connect camper</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7760,7 +7760,7 @@
           <t>interior mercedes sprinter van</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7793,7 +7793,7 @@
           <t>mercedes sprinter campervans</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7811,7 +7811,7 @@
       <c r="E81" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F81" s="7" t="n">
+      <c r="F81" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G81" t="inlineStr">
@@ -7826,7 +7826,7 @@
           <t>mercedes travel van</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7844,7 +7844,7 @@
       <c r="E82" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F82" s="7" t="n">
+      <c r="F82" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G82" t="inlineStr">
@@ -7859,7 +7859,7 @@
           <t>passenger sprinter standover height</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7910,7 +7910,7 @@
       <c r="E84" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="9" t="n">
         <v>62</v>
       </c>
       <c r="G84" t="inlineStr">
@@ -7925,7 +7925,7 @@
           <t>what is a sprinter van</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7943,7 +7943,7 @@
       <c r="E85" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G85" t="inlineStr">
@@ -7958,7 +7958,7 @@
           <t>mercedes sprinter conversion</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -7991,7 +7991,7 @@
           <t>mercedes sprinter 3500</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8024,7 +8024,7 @@
           <t>sprinter automatic</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8057,7 +8057,7 @@
           <t>mercedes benz passenger van</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8123,7 +8123,7 @@
           <t>ford transit van mpg</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8156,7 +8156,7 @@
           <t>transit vans</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8207,12 +8207,12 @@
       <c r="E93" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F93" s="7" t="n">
+      <c r="F93" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
           <t>camping van ford</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8255,7 +8255,7 @@
           <t>ford conversion van</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8288,7 +8288,7 @@
           <t>ford transit 4x4</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8306,7 +8306,7 @@
       <c r="E96" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F96" s="7" t="n">
+      <c r="F96" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G96" t="inlineStr">
@@ -8321,7 +8321,7 @@
           <t>ford transit all wheel drive</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8339,7 +8339,7 @@
       <c r="E97" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F97" s="7" t="n">
+      <c r="F97" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G97" t="inlineStr">
@@ -8354,7 +8354,7 @@
           <t>ford transit van awd</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8372,7 +8372,7 @@
       <c r="E98" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F98" s="7" t="n">
+      <c r="F98" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G98" t="inlineStr">
@@ -8387,7 +8387,7 @@
           <t>ford transit van conversion</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8420,7 +8420,7 @@
           <t>high roof cargo van</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8453,7 +8453,7 @@
           <t>mercedes benz sprinter camper</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8486,7 +8486,7 @@
           <t>mercedes benz sprinter camper van</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8519,7 +8519,7 @@
           <t>mercedes benz sprinter interior</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8552,7 +8552,7 @@
           <t>ram camper van</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8603,7 +8603,7 @@
       <c r="E105" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F105" s="7" t="n">
+      <c r="F105" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G105" t="inlineStr">
@@ -8618,7 +8618,7 @@
           <t>sprinter van dimensions</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8669,7 +8669,7 @@
       <c r="E107" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="F107" s="7" t="n">
+      <c r="F107" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G107" t="inlineStr">
@@ -8717,7 +8717,7 @@
           <t>campervan conversion ford transit</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8783,7 +8783,7 @@
           <t>sprinter conversion</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8801,7 +8801,7 @@
       <c r="E111" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F111" s="7" t="n">
+      <c r="F111" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G111" t="inlineStr">
@@ -8816,7 +8816,7 @@
           <t>mercedes sprinter van conversion</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8849,7 +8849,7 @@
           <t>custom sprinter van</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8882,7 +8882,7 @@
           <t>mb sprinter diesel</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8915,7 +8915,7 @@
           <t>mercedes sprinter cost</t>
         </is>
       </c>
-      <c r="B115" s="9" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -8936,9 +8936,9 @@
       <c r="F115" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G115" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
           <t>sprinter van cost</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9047,7 +9047,7 @@
           <t>ford transit 250 medium roof</t>
         </is>
       </c>
-      <c r="B119" s="9" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9080,7 +9080,7 @@
           <t>ford transit camper conversion</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9113,7 +9113,7 @@
           <t>ford transit connect camper van</t>
         </is>
       </c>
-      <c r="B121" s="9" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9146,7 +9146,7 @@
           <t>ford transit fuel economy</t>
         </is>
       </c>
-      <c r="B122" s="9" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9197,7 +9197,7 @@
       <c r="E123" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F123" s="7" t="n">
+      <c r="F123" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G123" t="inlineStr">
@@ -9230,7 +9230,7 @@
       <c r="E124" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F124" s="7" t="n">
+      <c r="F124" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G124" t="inlineStr">
@@ -9263,7 +9263,7 @@
       <c r="E125" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F125" s="7" t="n">
+      <c r="F125" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G125" t="inlineStr">
@@ -9278,7 +9278,7 @@
           <t>transit 350 xlt</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9311,7 +9311,7 @@
           <t>best van</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9329,7 +9329,7 @@
       <c r="E127" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F127" s="7" t="n">
+      <c r="F127" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -9398,9 +9398,9 @@
       <c r="F129" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
           <t>ford transit size specifications</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9428,7 +9428,7 @@
       <c r="E130" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F130" s="7" t="n">
+      <c r="F130" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G130" t="inlineStr">
@@ -9443,7 +9443,7 @@
           <t>ford transit sizes</t>
         </is>
       </c>
-      <c r="B131" s="9" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9461,7 +9461,7 @@
       <c r="E131" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F131" s="7" t="n">
+      <c r="F131" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G131" t="inlineStr">
@@ -9494,7 +9494,7 @@
       <c r="E132" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F132" s="7" t="n">
+      <c r="F132" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G132" t="inlineStr">
@@ -9575,7 +9575,7 @@
           <t>mercedes benz sprinter van interior</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9608,7 +9608,7 @@
           <t>mercedes sprinter travel van</t>
         </is>
       </c>
-      <c r="B136" s="9" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9674,7 +9674,7 @@
           <t>sprinter travel van</t>
         </is>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9695,9 +9695,9 @@
       <c r="F138" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G138" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       <c r="E139" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F139" s="7" t="n">
+      <c r="F139" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G139" t="inlineStr">
@@ -9758,7 +9758,7 @@
       <c r="E140" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F140" s="6" t="n">
+      <c r="F140" s="9" t="n">
         <v>51</v>
       </c>
       <c r="G140" t="inlineStr">
@@ -9806,7 +9806,7 @@
           <t>sprinter van accessories</t>
         </is>
       </c>
-      <c r="B142" s="9" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -9872,7 +9872,7 @@
           <t>best vans for van life</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -9959,9 +9959,9 @@
       <c r="F146" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
           <t>transit passenger van</t>
         </is>
       </c>
-      <c r="B148" s="9" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10022,7 +10022,7 @@
       <c r="E148" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F148" s="7" t="n">
+      <c r="F148" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G148" t="inlineStr">
@@ -10037,7 +10037,7 @@
           <t>ford transit campervan</t>
         </is>
       </c>
-      <c r="B149" s="9" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10055,7 +10055,7 @@
       <c r="E149" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F149" s="7" t="n">
+      <c r="F149" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G149" t="inlineStr">
@@ -10070,7 +10070,7 @@
           <t>converting ford transit</t>
         </is>
       </c>
-      <c r="B150" s="9" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10103,7 +10103,7 @@
           <t>transit camper van</t>
         </is>
       </c>
-      <c r="B151" s="9" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10121,12 +10121,12 @@
       <c r="E151" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F151" s="7" t="n">
+      <c r="F151" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10136,7 +10136,7 @@
           <t>ford transit conversion</t>
         </is>
       </c>
-      <c r="B152" s="9" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10169,7 +10169,7 @@
           <t>sprinter van with bathroom</t>
         </is>
       </c>
-      <c r="B153" s="9" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10289,9 +10289,9 @@
       <c r="F156" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10322,9 +10322,9 @@
       <c r="F157" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G157" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       <c r="E158" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F158" s="7" t="n">
+      <c r="F158" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G158" t="inlineStr">
@@ -10385,7 +10385,7 @@
       <c r="E159" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F159" s="6" t="n">
+      <c r="F159" s="9" t="n">
         <v>69</v>
       </c>
       <c r="G159" t="inlineStr">
@@ -10418,7 +10418,7 @@
       <c r="E160" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F160" s="6" t="n">
+      <c r="F160" s="9" t="n">
         <v>51</v>
       </c>
       <c r="G160" t="inlineStr">
@@ -10433,7 +10433,7 @@
           <t>dodge ram camper van</t>
         </is>
       </c>
-      <c r="B161" s="9" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10466,7 +10466,7 @@
           <t>ford transit 4wd</t>
         </is>
       </c>
-      <c r="B162" s="9" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10484,7 +10484,7 @@
       <c r="E162" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F162" s="7" t="n">
+      <c r="F162" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G162" t="inlineStr">
@@ -10499,7 +10499,7 @@
           <t>ford transit van 4 wheel drive</t>
         </is>
       </c>
-      <c r="B163" s="9" t="inlineStr">
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10517,7 +10517,7 @@
       <c r="E163" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F163" s="6" t="n">
+      <c r="F163" s="9" t="n">
         <v>52</v>
       </c>
       <c r="G163" t="inlineStr">
@@ -10532,7 +10532,7 @@
           <t>ford van hard to work on</t>
         </is>
       </c>
-      <c r="B164" s="9" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10565,7 +10565,7 @@
           <t>mercedes benz travel van</t>
         </is>
       </c>
-      <c r="B165" s="9" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10583,7 +10583,7 @@
       <c r="E165" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F165" s="7" t="n">
+      <c r="F165" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G165" t="inlineStr">
@@ -10598,7 +10598,7 @@
           <t>mercedes camper vans</t>
         </is>
       </c>
-      <c r="B166" s="9" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10616,7 +10616,7 @@
       <c r="E166" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F166" s="7" t="n">
+      <c r="F166" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G166" t="inlineStr">
@@ -10631,7 +10631,7 @@
           <t>mercedes sprinter campervan</t>
         </is>
       </c>
-      <c r="B167" s="9" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10649,7 +10649,7 @@
       <c r="E167" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F167" s="7" t="n">
+      <c r="F167" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G167" t="inlineStr">
@@ -10796,7 +10796,7 @@
           <t>sprinter 4x4</t>
         </is>
       </c>
-      <c r="B172" s="9" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10847,7 +10847,7 @@
       <c r="E173" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F173" s="7" t="n">
+      <c r="F173" s="6" t="n">
         <v>31</v>
       </c>
       <c r="G173" t="inlineStr">
@@ -10895,7 +10895,7 @@
           <t>van ford transit</t>
         </is>
       </c>
-      <c r="B175" s="9" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -10913,7 +10913,7 @@
       <c r="E175" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F175" s="6" t="n">
+      <c r="F175" s="9" t="n">
         <v>62</v>
       </c>
       <c r="G175" t="inlineStr">
@@ -10946,7 +10946,7 @@
       <c r="E176" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F176" s="6" t="n">
+      <c r="F176" s="9" t="n">
         <v>57</v>
       </c>
       <c r="G176" t="inlineStr">
@@ -10994,7 +10994,7 @@
           <t>vanlife outfitters</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -11012,7 +11012,7 @@
       <c r="E178" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="F178" s="6" t="n">
+      <c r="F178" s="9" t="n">
         <v>52</v>
       </c>
       <c r="G178" t="inlineStr">
@@ -11093,7 +11093,7 @@
           <t>ford transit seats</t>
         </is>
       </c>
-      <c r="B181" s="9" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11126,7 +11126,7 @@
           <t>sprinter luxury</t>
         </is>
       </c>
-      <c r="B182" s="9" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11159,7 +11159,7 @@
           <t>sprinter 4x4 sprinter</t>
         </is>
       </c>
-      <c r="B183" s="9" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11192,7 +11192,7 @@
           <t>sprinter interior</t>
         </is>
       </c>
-      <c r="B184" s="9" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11225,7 +11225,7 @@
           <t>mercedes conversion van</t>
         </is>
       </c>
-      <c r="B185" s="9" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11258,7 +11258,7 @@
           <t>mercedes camper van 4x4</t>
         </is>
       </c>
-      <c r="B186" s="9" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11276,7 +11276,7 @@
       <c r="E186" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F186" s="7" t="n">
+      <c r="F186" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G186" t="inlineStr">
@@ -11291,7 +11291,7 @@
           <t>mercedes sprinter 2019</t>
         </is>
       </c>
-      <c r="B187" s="9" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11324,7 +11324,7 @@
           <t>mercedes benz sprinter price</t>
         </is>
       </c>
-      <c r="B188" s="9" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11357,7 +11357,7 @@
           <t>sprinter van sizes</t>
         </is>
       </c>
-      <c r="B189" s="9" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11390,7 +11390,7 @@
           <t>cost of mercedes benz sprinter</t>
         </is>
       </c>
-      <c r="B190" s="9" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11543,9 +11543,9 @@
       <c r="F194" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G194" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
           <t>ford transit connect passenger van</t>
         </is>
       </c>
-      <c r="B195" s="9" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11573,7 +11573,7 @@
       <c r="E195" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F195" s="7" t="n">
+      <c r="F195" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G195" t="inlineStr">
@@ -11588,7 +11588,7 @@
           <t>transit trail</t>
         </is>
       </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11621,7 +11621,7 @@
           <t>gas mileage on a ford transit</t>
         </is>
       </c>
-      <c r="B197" s="9" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11654,7 +11654,7 @@
           <t>awd sprinter van</t>
         </is>
       </c>
-      <c r="B198" s="9" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11687,7 +11687,7 @@
           <t>sprinter van inside</t>
         </is>
       </c>
-      <c r="B199" s="9" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11720,7 +11720,7 @@
           <t>2025 mercedes benz sprinter specs</t>
         </is>
       </c>
-      <c r="B200" s="9" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11753,7 +11753,7 @@
           <t>4x4 camper van</t>
         </is>
       </c>
-      <c r="B201" s="9" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11786,7 +11786,7 @@
           <t>awd ford transit</t>
         </is>
       </c>
-      <c r="B202" s="9" t="inlineStr">
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -11852,7 +11852,7 @@
           <t>best van for van life</t>
         </is>
       </c>
-      <c r="B204" s="8" t="inlineStr">
+      <c r="B204" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -11903,7 +11903,7 @@
       <c r="E205" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F205" s="7" t="n">
+      <c r="F205" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G205" t="inlineStr">
@@ -11918,7 +11918,7 @@
           <t>campervans ford</t>
         </is>
       </c>
-      <c r="B206" s="9" t="inlineStr">
+      <c r="B206" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12002,7 +12002,7 @@
       <c r="E208" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F208" s="6" t="n">
+      <c r="F208" s="9" t="n">
         <v>63</v>
       </c>
       <c r="G208" t="inlineStr">
@@ -12017,7 +12017,7 @@
           <t>for transit camper van</t>
         </is>
       </c>
-      <c r="B209" s="9" t="inlineStr">
+      <c r="B209" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12050,7 +12050,7 @@
           <t>for transit van</t>
         </is>
       </c>
-      <c r="B210" s="9" t="inlineStr">
+      <c r="B210" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12068,7 +12068,7 @@
       <c r="E210" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F210" s="7" t="n">
+      <c r="F210" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G210" t="inlineStr">
@@ -12083,7 +12083,7 @@
           <t>ford transit high roof extended</t>
         </is>
       </c>
-      <c r="B211" s="9" t="inlineStr">
+      <c r="B211" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12116,7 +12116,7 @@
           <t>ford transit medium roof</t>
         </is>
       </c>
-      <c r="B212" s="9" t="inlineStr">
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12137,9 +12137,9 @@
       <c r="F212" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G212" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12149,7 @@
           <t>ford transit medium roof height</t>
         </is>
       </c>
-      <c r="B213" s="9" t="inlineStr">
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12182,7 +12182,7 @@
           <t>ford transit van 4x4</t>
         </is>
       </c>
-      <c r="B214" s="9" t="inlineStr">
+      <c r="B214" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12200,7 +12200,7 @@
       <c r="E214" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F214" s="7" t="n">
+      <c r="F214" s="6" t="n">
         <v>49</v>
       </c>
       <c r="G214" t="inlineStr">
@@ -12215,7 +12215,7 @@
           <t>ford transit van camper</t>
         </is>
       </c>
-      <c r="B215" s="9" t="inlineStr">
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12233,7 +12233,7 @@
       <c r="E215" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F215" s="7" t="n">
+      <c r="F215" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G215" t="inlineStr">
@@ -12266,7 +12266,7 @@
       <c r="E216" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F216" s="6" t="n">
+      <c r="F216" s="9" t="n">
         <v>66</v>
       </c>
       <c r="G216" t="inlineStr">
@@ -12299,7 +12299,7 @@
       <c r="E217" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F217" s="7" t="n">
+      <c r="F217" s="6" t="n">
         <v>37</v>
       </c>
       <c r="G217" t="inlineStr">
@@ -12314,7 +12314,7 @@
           <t>mercedes camping van</t>
         </is>
       </c>
-      <c r="B218" s="9" t="inlineStr">
+      <c r="B218" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12332,7 +12332,7 @@
       <c r="E218" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F218" s="7" t="n">
+      <c r="F218" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G218" t="inlineStr">
@@ -12347,7 +12347,7 @@
           <t>mercedes sprinter camper interior</t>
         </is>
       </c>
-      <c r="B219" s="9" t="inlineStr">
+      <c r="B219" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12380,7 +12380,7 @@
           <t>mercedes sprinter camper vans</t>
         </is>
       </c>
-      <c r="B220" s="9" t="inlineStr">
+      <c r="B220" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12398,7 +12398,7 @@
       <c r="E220" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F220" s="7" t="n">
+      <c r="F220" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G220" t="inlineStr">
@@ -12413,7 +12413,7 @@
           <t>mercedes sprinter van cost</t>
         </is>
       </c>
-      <c r="B221" s="9" t="inlineStr">
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12431,12 +12431,12 @@
       <c r="E221" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F221" s="7" t="n">
+      <c r="F221" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="G221" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
           <t>mercedes sprinter van dimensions</t>
         </is>
       </c>
-      <c r="B222" s="9" t="inlineStr">
+      <c r="B222" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12497,7 +12497,7 @@
       <c r="E223" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F223" s="7" t="n">
+      <c r="F223" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G223" t="inlineStr">
@@ -12512,7 +12512,7 @@
           <t>ram promaster camper</t>
         </is>
       </c>
-      <c r="B224" s="9" t="inlineStr">
+      <c r="B224" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12545,7 +12545,7 @@
           <t>ram promaster camper van</t>
         </is>
       </c>
-      <c r="B225" s="9" t="inlineStr">
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12578,7 +12578,7 @@
           <t>sprinter conversion van</t>
         </is>
       </c>
-      <c r="B226" s="9" t="inlineStr">
+      <c r="B226" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12596,7 +12596,7 @@
       <c r="E226" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F226" s="7" t="n">
+      <c r="F226" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G226" t="inlineStr">
@@ -12611,7 +12611,7 @@
           <t>sprinter reclining seats 4 seater</t>
         </is>
       </c>
-      <c r="B227" s="9" t="inlineStr">
+      <c r="B227" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12644,7 +12644,7 @@
           <t>sprinter seats</t>
         </is>
       </c>
-      <c r="B228" s="9" t="inlineStr">
+      <c r="B228" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12665,9 +12665,9 @@
       <c r="F228" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G228" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
           <t>sprinter source</t>
         </is>
       </c>
-      <c r="B229" s="9" t="inlineStr">
+      <c r="B229" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12710,7 +12710,7 @@
           <t>sprinter van mpg</t>
         </is>
       </c>
-      <c r="B230" s="9" t="inlineStr">
+      <c r="B230" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12743,7 +12743,7 @@
           <t>sprinter van seats</t>
         </is>
       </c>
-      <c r="B231" s="9" t="inlineStr">
+      <c r="B231" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12776,7 +12776,7 @@
           <t>sprinter van width</t>
         </is>
       </c>
-      <c r="B232" s="9" t="inlineStr">
+      <c r="B232" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -12863,9 +12863,9 @@
       <c r="F234" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G234" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       <c r="E237" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F237" s="7" t="n">
+      <c r="F237" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G237" t="inlineStr">
@@ -12992,7 +12992,7 @@
       <c r="E238" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F238" s="7" t="n">
+      <c r="F238" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G238" t="inlineStr">
@@ -13007,7 +13007,7 @@
           <t>van sprinter 4x4</t>
         </is>
       </c>
-      <c r="B239" s="9" t="inlineStr">
+      <c r="B239" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13058,7 +13058,7 @@
       <c r="E240" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="F240" s="7" t="n">
+      <c r="F240" s="6" t="n">
         <v>39</v>
       </c>
       <c r="G240" t="inlineStr">
@@ -13106,7 +13106,7 @@
           <t>benz sprinter limo</t>
         </is>
       </c>
-      <c r="B242" s="9" t="inlineStr">
+      <c r="B242" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13157,7 +13157,7 @@
       <c r="E243" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F243" s="7" t="n">
+      <c r="F243" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G243" t="inlineStr">
@@ -13172,7 +13172,7 @@
           <t>mercedes benz sprinter van price</t>
         </is>
       </c>
-      <c r="B244" s="9" t="inlineStr">
+      <c r="B244" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13193,9 +13193,9 @@
       <c r="F244" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G244" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -13205,7 +13205,7 @@
           <t>custom sprinter</t>
         </is>
       </c>
-      <c r="B245" s="9" t="inlineStr">
+      <c r="B245" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13223,7 +13223,7 @@
       <c r="E245" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F245" s="7" t="n">
+      <c r="F245" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G245" t="inlineStr">
@@ -13238,7 +13238,7 @@
           <t>mb sprinter 4x4 camper</t>
         </is>
       </c>
-      <c r="B246" s="9" t="inlineStr">
+      <c r="B246" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13271,7 +13271,7 @@
           <t>mercedes sprinter camper conversion</t>
         </is>
       </c>
-      <c r="B247" s="9" t="inlineStr">
+      <c r="B247" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13304,7 +13304,7 @@
           <t>mercedes sprinter van camper conversions</t>
         </is>
       </c>
-      <c r="B248" s="9" t="inlineStr">
+      <c r="B248" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13337,7 +13337,7 @@
           <t>sprinter van build</t>
         </is>
       </c>
-      <c r="B249" s="9" t="inlineStr">
+      <c r="B249" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13370,7 +13370,7 @@
           <t>how much is a sprinter van</t>
         </is>
       </c>
-      <c r="B250" s="9" t="inlineStr">
+      <c r="B250" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13403,7 +13403,7 @@
           <t>sprinter van parts</t>
         </is>
       </c>
-      <c r="B251" s="9" t="inlineStr">
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13436,7 +13436,7 @@
           <t>van life essentials</t>
         </is>
       </c>
-      <c r="B252" s="8" t="inlineStr">
+      <c r="B252" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -13490,9 +13490,9 @@
       <c r="F253" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G253" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
           <t>ford transit accessories</t>
         </is>
       </c>
-      <c r="B255" s="9" t="inlineStr">
+      <c r="B255" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13556,9 +13556,9 @@
       <c r="F255" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G255" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13568,7 @@
           <t>ford transit van camper conversion</t>
         </is>
       </c>
-      <c r="B256" s="9" t="inlineStr">
+      <c r="B256" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13601,7 +13601,7 @@
           <t>ford transit van inside dimensions</t>
         </is>
       </c>
-      <c r="B257" s="9" t="inlineStr">
+      <c r="B257" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13667,7 +13667,7 @@
           <t>most reliable cargo van</t>
         </is>
       </c>
-      <c r="B259" s="9" t="inlineStr">
+      <c r="B259" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13700,7 +13700,7 @@
           <t>mercedes 2500 van</t>
         </is>
       </c>
-      <c r="B260" s="9" t="inlineStr">
+      <c r="B260" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13733,7 +13733,7 @@
           <t>ford transit models</t>
         </is>
       </c>
-      <c r="B261" s="9" t="inlineStr">
+      <c r="B261" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13853,9 +13853,9 @@
       <c r="F264" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G264" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13865,7 +13865,7 @@
           <t>15 passenger ford transit van</t>
         </is>
       </c>
-      <c r="B265" s="9" t="inlineStr">
+      <c r="B265" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13883,7 +13883,7 @@
       <c r="E265" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F265" s="7" t="n">
+      <c r="F265" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G265" t="inlineStr">
@@ -13898,7 +13898,7 @@
           <t>4 by 4 sprinter</t>
         </is>
       </c>
-      <c r="B266" s="9" t="inlineStr">
+      <c r="B266" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13964,7 +13964,7 @@
           <t>4x4 mercedes sprinter</t>
         </is>
       </c>
-      <c r="B268" s="9" t="inlineStr">
+      <c r="B268" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -13982,7 +13982,7 @@
       <c r="E268" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F268" s="7" t="n">
+      <c r="F268" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G268" t="inlineStr">
@@ -13997,7 +13997,7 @@
           <t>4x4 sprinter van</t>
         </is>
       </c>
-      <c r="B269" s="9" t="inlineStr">
+      <c r="B269" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14117,9 +14117,9 @@
       <c r="F272" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G272" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
           <t>camper sprinter van</t>
         </is>
       </c>
-      <c r="B275" s="9" t="inlineStr">
+      <c r="B275" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14279,7 +14279,7 @@
       <c r="E277" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F277" s="7" t="n">
+      <c r="F277" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G277" t="inlineStr">
@@ -14345,7 +14345,7 @@
       <c r="E279" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F279" s="6" t="n">
+      <c r="F279" s="9" t="n">
         <v>55</v>
       </c>
       <c r="G279" t="inlineStr">
@@ -14378,7 +14378,7 @@
       <c r="E280" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F280" s="6" t="n">
+      <c r="F280" s="9" t="n">
         <v>56</v>
       </c>
       <c r="G280" t="inlineStr">
@@ -14411,7 +14411,7 @@
       <c r="E281" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F281" s="6" t="n">
+      <c r="F281" s="9" t="n">
         <v>50</v>
       </c>
       <c r="G281" t="inlineStr">
@@ -14444,7 +14444,7 @@
       <c r="E282" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F282" s="6" t="n">
+      <c r="F282" s="9" t="n">
         <v>53</v>
       </c>
       <c r="G282" t="inlineStr">
@@ -14492,7 +14492,7 @@
           <t>ford transit 12 passenger van interior</t>
         </is>
       </c>
-      <c r="B284" s="9" t="inlineStr">
+      <c r="B284" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14525,7 +14525,7 @@
           <t>ford transit 15 passenger van interior</t>
         </is>
       </c>
-      <c r="B285" s="9" t="inlineStr">
+      <c r="B285" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14543,7 +14543,7 @@
       <c r="E285" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F285" s="7" t="n">
+      <c r="F285" s="6" t="n">
         <v>30</v>
       </c>
       <c r="G285" t="inlineStr">
@@ -14558,7 +14558,7 @@
           <t>ford transit build</t>
         </is>
       </c>
-      <c r="B286" s="9" t="inlineStr">
+      <c r="B286" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14591,7 +14591,7 @@
           <t>ford transit camper vans</t>
         </is>
       </c>
-      <c r="B287" s="9" t="inlineStr">
+      <c r="B287" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14624,7 +14624,7 @@
           <t>ford transit campervan conversion</t>
         </is>
       </c>
-      <c r="B288" s="9" t="inlineStr">
+      <c r="B288" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14657,7 +14657,7 @@
           <t>ford transit height</t>
         </is>
       </c>
-      <c r="B289" s="9" t="inlineStr">
+      <c r="B289" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14690,7 +14690,7 @@
           <t>ford transit interior dimensions</t>
         </is>
       </c>
-      <c r="B290" s="9" t="inlineStr">
+      <c r="B290" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14723,7 +14723,7 @@
           <t>ford transit luxury adventure office</t>
         </is>
       </c>
-      <c r="B291" s="9" t="inlineStr">
+      <c r="B291" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14756,7 +14756,7 @@
           <t>ford transit van high roof</t>
         </is>
       </c>
-      <c r="B292" s="9" t="inlineStr">
+      <c r="B292" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14774,7 +14774,7 @@
       <c r="E292" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F292" s="7" t="n">
+      <c r="F292" s="6" t="n">
         <v>44</v>
       </c>
       <c r="G292" t="inlineStr">
@@ -14789,7 +14789,7 @@
           <t>ford transit van interior dimensions</t>
         </is>
       </c>
-      <c r="B293" s="9" t="inlineStr">
+      <c r="B293" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14822,7 +14822,7 @@
           <t>ford van types</t>
         </is>
       </c>
-      <c r="B294" s="9" t="inlineStr">
+      <c r="B294" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14855,7 +14855,7 @@
           <t>high roof van</t>
         </is>
       </c>
-      <c r="B295" s="9" t="inlineStr">
+      <c r="B295" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14921,7 +14921,7 @@
           <t>mercedes benz sprinter conversion</t>
         </is>
       </c>
-      <c r="B297" s="9" t="inlineStr">
+      <c r="B297" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14954,7 +14954,7 @@
           <t>mercedes benz sprinter size</t>
         </is>
       </c>
-      <c r="B298" s="9" t="inlineStr">
+      <c r="B298" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -14987,7 +14987,7 @@
           <t>mercedes sprinter 4x4 camper</t>
         </is>
       </c>
-      <c r="B299" s="9" t="inlineStr">
+      <c r="B299" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15020,7 +15020,7 @@
           <t>mercedes sprinter dimensions</t>
         </is>
       </c>
-      <c r="B300" s="9" t="inlineStr">
+      <c r="B300" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15053,7 +15053,7 @@
           <t>mercedes sprinter length</t>
         </is>
       </c>
-      <c r="B301" s="9" t="inlineStr">
+      <c r="B301" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15086,7 +15086,7 @@
           <t>mercedes sprinter recreational vehicle</t>
         </is>
       </c>
-      <c r="B302" s="9" t="inlineStr">
+      <c r="B302" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15104,7 +15104,7 @@
       <c r="E302" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F302" s="7" t="n">
+      <c r="F302" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G302" t="inlineStr">
@@ -15119,7 +15119,7 @@
           <t>mercedes transit van dimensions</t>
         </is>
       </c>
-      <c r="B303" s="9" t="inlineStr">
+      <c r="B303" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15203,7 +15203,7 @@
       <c r="E305" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F305" s="7" t="n">
+      <c r="F305" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G305" t="inlineStr">
@@ -15218,7 +15218,7 @@
           <t>small sprinter van</t>
         </is>
       </c>
-      <c r="B306" s="9" t="inlineStr">
+      <c r="B306" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15269,7 +15269,7 @@
       <c r="E307" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F307" s="7" t="n">
+      <c r="F307" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G307" t="inlineStr">
@@ -15284,7 +15284,7 @@
           <t>sprinter camper vans</t>
         </is>
       </c>
-      <c r="B308" s="9" t="inlineStr">
+      <c r="B308" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15302,7 +15302,7 @@
       <c r="E308" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F308" s="7" t="n">
+      <c r="F308" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G308" t="inlineStr">
@@ -15317,7 +15317,7 @@
           <t>sprinter recreational vehicle</t>
         </is>
       </c>
-      <c r="B309" s="9" t="inlineStr">
+      <c r="B309" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15350,7 +15350,7 @@
           <t>sprinter van 4x4</t>
         </is>
       </c>
-      <c r="B310" s="9" t="inlineStr">
+      <c r="B310" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15368,7 +15368,7 @@
       <c r="E310" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F310" s="7" t="n">
+      <c r="F310" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G310" t="inlineStr">
@@ -15383,7 +15383,7 @@
           <t>sprinter van length</t>
         </is>
       </c>
-      <c r="B311" s="9" t="inlineStr">
+      <c r="B311" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15416,7 +15416,7 @@
           <t>sprinter van price</t>
         </is>
       </c>
-      <c r="B312" s="9" t="inlineStr">
+      <c r="B312" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15449,7 +15449,7 @@
           <t>sprinter with bathroom</t>
         </is>
       </c>
-      <c r="B313" s="9" t="inlineStr">
+      <c r="B313" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15482,7 +15482,7 @@
           <t>transit van camper</t>
         </is>
       </c>
-      <c r="B314" s="9" t="inlineStr">
+      <c r="B314" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15599,7 +15599,7 @@
       <c r="E317" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F317" s="6" t="n">
+      <c r="F317" s="9" t="n">
         <v>54</v>
       </c>
       <c r="G317" t="inlineStr">
@@ -15632,7 +15632,7 @@
       <c r="E318" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="F318" s="6" t="n">
+      <c r="F318" s="9" t="n">
         <v>64</v>
       </c>
       <c r="G318" t="inlineStr">
@@ -15647,7 +15647,7 @@
           <t>van life news</t>
         </is>
       </c>
-      <c r="B319" s="8" t="inlineStr">
+      <c r="B319" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -15812,7 +15812,7 @@
           <t>mercedes benz limo sprinter</t>
         </is>
       </c>
-      <c r="B324" s="9" t="inlineStr">
+      <c r="B324" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15896,7 +15896,7 @@
       <c r="E326" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F326" s="7" t="n">
+      <c r="F326" s="6" t="n">
         <v>46</v>
       </c>
       <c r="G326" t="inlineStr">
@@ -15911,7 +15911,7 @@
           <t>diy van conversions</t>
         </is>
       </c>
-      <c r="B327" s="8" t="inlineStr">
+      <c r="B327" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -15932,9 +15932,9 @@
       <c r="F327" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G327" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -15944,7 +15944,7 @@
           <t>ford transit van shelving</t>
         </is>
       </c>
-      <c r="B328" s="9" t="inlineStr">
+      <c r="B328" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15977,7 +15977,7 @@
           <t>ford transit shelving</t>
         </is>
       </c>
-      <c r="B329" s="9" t="inlineStr">
+      <c r="B329" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -15998,9 +15998,9 @@
       <c r="F329" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G329" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16010,7 @@
           <t>black sprinter van</t>
         </is>
       </c>
-      <c r="B330" s="9" t="inlineStr">
+      <c r="B330" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16043,7 +16043,7 @@
           <t>black mercedes sprinter van</t>
         </is>
       </c>
-      <c r="B331" s="9" t="inlineStr">
+      <c r="B331" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16076,7 +16076,7 @@
           <t>4 wheel drive mercedes camper van</t>
         </is>
       </c>
-      <c r="B332" s="9" t="inlineStr">
+      <c r="B332" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16109,7 +16109,7 @@
           <t>mb 3500 sprinter</t>
         </is>
       </c>
-      <c r="B333" s="9" t="inlineStr">
+      <c r="B333" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16142,7 +16142,7 @@
           <t>mercedes sprinter van life</t>
         </is>
       </c>
-      <c r="B334" s="8" t="inlineStr">
+      <c r="B334" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -16163,9 +16163,9 @@
       <c r="F334" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G334" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
           <t>sprinter accessories</t>
         </is>
       </c>
-      <c r="B335" s="9" t="inlineStr">
+      <c r="B335" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16208,7 +16208,7 @@
           <t>sprinter price</t>
         </is>
       </c>
-      <c r="B336" s="9" t="inlineStr">
+      <c r="B336" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16241,7 +16241,7 @@
           <t>best van for camper conversion</t>
         </is>
       </c>
-      <c r="B337" s="9" t="inlineStr">
+      <c r="B337" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16295,9 +16295,9 @@
       <c r="F338" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G338" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
           <t>diy overland trailer</t>
         </is>
       </c>
-      <c r="B340" s="8" t="inlineStr">
+      <c r="B340" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -16373,7 +16373,7 @@
           <t>ford transit extended high roof</t>
         </is>
       </c>
-      <c r="B341" s="9" t="inlineStr">
+      <c r="B341" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16406,7 +16406,7 @@
           <t>ford transit van accessories</t>
         </is>
       </c>
-      <c r="B342" s="9" t="inlineStr">
+      <c r="B342" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16439,7 +16439,7 @@
           <t>ford transit mid roof</t>
         </is>
       </c>
-      <c r="B343" s="9" t="inlineStr">
+      <c r="B343" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16472,7 +16472,7 @@
           <t>ford transit mileage</t>
         </is>
       </c>
-      <c r="B344" s="9" t="inlineStr">
+      <c r="B344" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16505,7 +16505,7 @@
           <t>ford transit van fuel consumption</t>
         </is>
       </c>
-      <c r="B345" s="9" t="inlineStr">
+      <c r="B345" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16538,7 +16538,7 @@
           <t>most reliable van</t>
         </is>
       </c>
-      <c r="B346" s="9" t="inlineStr">
+      <c r="B346" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16589,7 +16589,7 @@
       <c r="E347" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F347" s="7" t="n">
+      <c r="F347" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G347" t="inlineStr">
@@ -16637,7 +16637,7 @@
           <t>price sprinter</t>
         </is>
       </c>
-      <c r="B349" s="9" t="inlineStr">
+      <c r="B349" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16670,7 +16670,7 @@
           <t>mercedes 2500 sprinter</t>
         </is>
       </c>
-      <c r="B350" s="9" t="inlineStr">
+      <c r="B350" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16703,7 +16703,7 @@
           <t>inside luxury mercedes sprinter van</t>
         </is>
       </c>
-      <c r="B351" s="9" t="inlineStr">
+      <c r="B351" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16721,7 +16721,7 @@
       <c r="E351" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F351" s="7" t="n">
+      <c r="F351" s="6" t="n">
         <v>32</v>
       </c>
       <c r="G351" t="inlineStr">
@@ -16736,7 +16736,7 @@
           <t>van price</t>
         </is>
       </c>
-      <c r="B352" s="9" t="inlineStr">
+      <c r="B352" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16754,7 +16754,7 @@
       <c r="E352" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F352" s="7" t="n">
+      <c r="F352" s="6" t="n">
         <v>48</v>
       </c>
       <c r="G352" t="inlineStr">
@@ -16769,7 +16769,7 @@
           <t>4 wheel drive sprinter van</t>
         </is>
       </c>
-      <c r="B353" s="9" t="inlineStr">
+      <c r="B353" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16802,7 +16802,7 @@
           <t>4x4 sprinter</t>
         </is>
       </c>
-      <c r="B354" s="9" t="inlineStr">
+      <c r="B354" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -16820,7 +16820,7 @@
       <c r="E354" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F354" s="7" t="n">
+      <c r="F354" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G354" t="inlineStr">
@@ -16835,7 +16835,7 @@
           <t>4x4 van conversion</t>
         </is>
       </c>
-      <c r="B355" s="9" t="inlineStr">
+      <c r="B355" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17000,7 +17000,7 @@
           <t>best mpg van</t>
         </is>
       </c>
-      <c r="B360" s="9" t="inlineStr">
+      <c r="B360" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17021,9 +17021,9 @@
       <c r="F360" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G360" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -17033,7 +17033,7 @@
           <t>best van life vans</t>
         </is>
       </c>
-      <c r="B361" s="8" t="inlineStr">
+      <c r="B361" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -17054,9 +17054,9 @@
       <c r="F361" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G361" s="10" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       <c r="E362" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F362" s="7" t="n">
+      <c r="F362" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G362" t="inlineStr">
@@ -17099,7 +17099,7 @@
           <t>camper sprinter</t>
         </is>
       </c>
-      <c r="B363" s="9" t="inlineStr">
+      <c r="B363" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17117,7 +17117,7 @@
       <c r="E363" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F363" s="7" t="n">
+      <c r="F363" s="6" t="n">
         <v>34</v>
       </c>
       <c r="G363" t="inlineStr">
@@ -17249,7 +17249,7 @@
       <c r="E367" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F367" s="7" t="n">
+      <c r="F367" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G367" t="inlineStr">
@@ -17315,7 +17315,7 @@
       <c r="E369" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F369" s="6" t="n">
+      <c r="F369" s="9" t="n">
         <v>57</v>
       </c>
       <c r="G369" t="inlineStr">
@@ -17330,7 +17330,7 @@
           <t>converted sprinter van</t>
         </is>
       </c>
-      <c r="B370" s="9" t="inlineStr">
+      <c r="B370" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17381,7 +17381,7 @@
       <c r="E371" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F371" s="6" t="n">
+      <c r="F371" s="9" t="n">
         <v>55</v>
       </c>
       <c r="G371" t="inlineStr">
@@ -17429,7 +17429,7 @@
           <t>dimensions sprinter mercedes</t>
         </is>
       </c>
-      <c r="B373" s="9" t="inlineStr">
+      <c r="B373" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17462,7 +17462,7 @@
           <t>diy camper van</t>
         </is>
       </c>
-      <c r="B374" s="8" t="inlineStr">
+      <c r="B374" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -17495,7 +17495,7 @@
           <t>diy van</t>
         </is>
       </c>
-      <c r="B375" s="8" t="inlineStr">
+      <c r="B375" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -17513,12 +17513,12 @@
       <c r="E375" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F375" s="7" t="n">
+      <c r="F375" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G375" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17528,7 @@
           <t>dodge ram van 2026</t>
         </is>
       </c>
-      <c r="B376" s="9" t="inlineStr">
+      <c r="B376" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17546,7 +17546,7 @@
       <c r="E376" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F376" s="7" t="n">
+      <c r="F376" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G376" t="inlineStr">
@@ -17561,7 +17561,7 @@
           <t>ford transit 4 wheel drive</t>
         </is>
       </c>
-      <c r="B377" s="9" t="inlineStr">
+      <c r="B377" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17579,7 +17579,7 @@
       <c r="E377" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F377" s="7" t="n">
+      <c r="F377" s="6" t="n">
         <v>43</v>
       </c>
       <c r="G377" t="inlineStr">
@@ -17594,7 +17594,7 @@
           <t>ford transit extended length</t>
         </is>
       </c>
-      <c r="B378" s="9" t="inlineStr">
+      <c r="B378" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17627,7 +17627,7 @@
           <t>ford transit seat</t>
         </is>
       </c>
-      <c r="B379" s="9" t="inlineStr">
+      <c r="B379" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17660,7 +17660,7 @@
           <t>ford transit seating</t>
         </is>
       </c>
-      <c r="B380" s="9" t="inlineStr">
+      <c r="B380" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17693,7 +17693,7 @@
           <t>ford transit van build</t>
         </is>
       </c>
-      <c r="B381" s="9" t="inlineStr">
+      <c r="B381" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17744,7 +17744,7 @@
       <c r="E382" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F382" s="7" t="n">
+      <c r="F382" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G382" t="inlineStr">
@@ -17780,9 +17780,9 @@
       <c r="F383" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G383" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -17792,7 +17792,7 @@
           <t>inside of a sprinter van</t>
         </is>
       </c>
-      <c r="B384" s="9" t="inlineStr">
+      <c r="B384" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17843,7 +17843,7 @@
       <c r="E385" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F385" s="7" t="n">
+      <c r="F385" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G385" t="inlineStr">
@@ -17858,7 +17858,7 @@
           <t>kamper mercedes sprinter</t>
         </is>
       </c>
-      <c r="B386" s="9" t="inlineStr">
+      <c r="B386" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -17909,7 +17909,7 @@
       <c r="E387" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F387" s="7" t="n">
+      <c r="F387" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G387" t="inlineStr">
@@ -17942,7 +17942,7 @@
       <c r="E388" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F388" s="7" t="n">
+      <c r="F388" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G388" t="inlineStr">
@@ -17975,7 +17975,7 @@
       <c r="E389" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F389" s="6" t="n">
+      <c r="F389" s="9" t="n">
         <v>51</v>
       </c>
       <c r="G389" t="inlineStr">
@@ -17990,7 +17990,7 @@
           <t>mercedes benz sprinter limo</t>
         </is>
       </c>
-      <c r="B390" s="9" t="inlineStr">
+      <c r="B390" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18023,7 +18023,7 @@
           <t>mercedes benz sprinter van dimensions</t>
         </is>
       </c>
-      <c r="B391" s="9" t="inlineStr">
+      <c r="B391" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18056,7 +18056,7 @@
           <t>mercedes sprinter 4x4 automatic</t>
         </is>
       </c>
-      <c r="B392" s="9" t="inlineStr">
+      <c r="B392" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18074,7 +18074,7 @@
       <c r="E392" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F392" s="7" t="n">
+      <c r="F392" s="6" t="n">
         <v>33</v>
       </c>
       <c r="G392" t="inlineStr">
@@ -18089,7 +18089,7 @@
           <t>mercedes sprinter camping van</t>
         </is>
       </c>
-      <c r="B393" s="9" t="inlineStr">
+      <c r="B393" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18122,7 +18122,7 @@
           <t>mercedes sprinter msrp</t>
         </is>
       </c>
-      <c r="B394" s="9" t="inlineStr">
+      <c r="B394" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18155,7 +18155,7 @@
           <t>mercedes sprinter width</t>
         </is>
       </c>
-      <c r="B395" s="9" t="inlineStr">
+      <c r="B395" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18188,7 +18188,7 @@
           <t>mercedes van 4x4 sprinter</t>
         </is>
       </c>
-      <c r="B396" s="9" t="inlineStr">
+      <c r="B396" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18206,7 +18206,7 @@
       <c r="E396" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F396" s="7" t="n">
+      <c r="F396" s="6" t="n">
         <v>41</v>
       </c>
       <c r="G396" t="inlineStr">
@@ -18221,7 +18221,7 @@
           <t>mercedes van interior</t>
         </is>
       </c>
-      <c r="B397" s="9" t="inlineStr">
+      <c r="B397" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18353,7 +18353,7 @@
           <t>ram promaster camper vans</t>
         </is>
       </c>
-      <c r="B401" s="9" t="inlineStr">
+      <c r="B401" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18437,7 +18437,7 @@
       <c r="E403" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F403" s="7" t="n">
+      <c r="F403" s="6" t="n">
         <v>38</v>
       </c>
       <c r="G403" t="inlineStr">
@@ -18452,7 +18452,7 @@
           <t>sprinter 144</t>
         </is>
       </c>
-      <c r="B404" s="9" t="inlineStr">
+      <c r="B404" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18485,7 +18485,7 @@
           <t>sprinter 170</t>
         </is>
       </c>
-      <c r="B405" s="9" t="inlineStr">
+      <c r="B405" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18518,7 +18518,7 @@
           <t>sprinter camper van mercedes</t>
         </is>
       </c>
-      <c r="B406" s="9" t="inlineStr">
+      <c r="B406" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18551,7 +18551,7 @@
           <t>sprinter travel vans</t>
         </is>
       </c>
-      <c r="B407" s="9" t="inlineStr">
+      <c r="B407" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18569,7 +18569,7 @@
       <c r="E407" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F407" s="7" t="n">
+      <c r="F407" s="6" t="n">
         <v>35</v>
       </c>
       <c r="G407" t="inlineStr">
@@ -18584,7 +18584,7 @@
           <t>sprinter van conversions</t>
         </is>
       </c>
-      <c r="B408" s="9" t="inlineStr">
+      <c r="B408" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18602,7 +18602,7 @@
       <c r="E408" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F408" s="7" t="n">
+      <c r="F408" s="6" t="n">
         <v>45</v>
       </c>
       <c r="G408" t="inlineStr">
@@ -18617,7 +18617,7 @@
           <t>sprinter van height</t>
         </is>
       </c>
-      <c r="B409" s="9" t="inlineStr">
+      <c r="B409" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18650,7 +18650,7 @@
           <t>sprinter van length in feet</t>
         </is>
       </c>
-      <c r="B410" s="9" t="inlineStr">
+      <c r="B410" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18800,7 +18800,7 @@
       <c r="E414" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F414" s="6" t="n">
+      <c r="F414" s="9" t="n">
         <v>57</v>
       </c>
       <c r="G414" t="inlineStr">
@@ -18848,7 +18848,7 @@
           <t>van ford camper</t>
         </is>
       </c>
-      <c r="B416" s="9" t="inlineStr">
+      <c r="B416" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -18881,7 +18881,7 @@
           <t>van life van</t>
         </is>
       </c>
-      <c r="B417" s="8" t="inlineStr">
+      <c r="B417" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -18914,7 +18914,7 @@
           <t>van life vans</t>
         </is>
       </c>
-      <c r="B418" s="8" t="inlineStr">
+      <c r="B418" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -18932,7 +18932,7 @@
       <c r="E418" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="F418" s="7" t="n">
+      <c r="F418" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G418" s="10" t="inlineStr">
@@ -19001,9 +19001,9 @@
       <c r="F420" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G420" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
           <t>camper van diy</t>
         </is>
       </c>
-      <c r="B423" s="8" t="inlineStr">
+      <c r="B423" s="7" t="inlineStr">
         <is>
           <t>Van Life &amp; Planning</t>
         </is>
@@ -19178,7 +19178,7 @@
           <t>ford transit racks</t>
         </is>
       </c>
-      <c r="B426" s="9" t="inlineStr">
+      <c r="B426" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19199,9 +19199,9 @@
       <c r="F426" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="G426" s="10" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -19211,7 +19211,7 @@
           <t>executive sprinter van</t>
         </is>
       </c>
-      <c r="B427" s="9" t="inlineStr">
+      <c r="B427" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19244,7 +19244,7 @@
           <t>sprinter build</t>
         </is>
       </c>
-      <c r="B428" s="9" t="inlineStr">
+      <c r="B428" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19277,7 +19277,7 @@
           <t>mercedes custom van</t>
         </is>
       </c>
-      <c r="B429" s="9" t="inlineStr">
+      <c r="B429" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19310,7 +19310,7 @@
           <t>2019 sprinter van</t>
         </is>
       </c>
-      <c r="B430" s="9" t="inlineStr">
+      <c r="B430" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19343,7 +19343,7 @@
           <t>new sprinter van</t>
         </is>
       </c>
-      <c r="B431" s="9" t="inlineStr">
+      <c r="B431" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19376,7 +19376,7 @@
           <t>sprinter diesel</t>
         </is>
       </c>
-      <c r="B432" s="9" t="inlineStr">
+      <c r="B432" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19409,7 +19409,7 @@
           <t>diesel sprinter van</t>
         </is>
       </c>
-      <c r="B433" s="9" t="inlineStr">
+      <c r="B433" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19442,7 +19442,7 @@
           <t>sprinter van 2500</t>
         </is>
       </c>
-      <c r="B434" s="9" t="inlineStr">
+      <c r="B434" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19475,7 +19475,7 @@
           <t>sprinter van 3500</t>
         </is>
       </c>
-      <c r="B435" s="9" t="inlineStr">
+      <c r="B435" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19508,7 +19508,7 @@
           <t>convert a sprinter van</t>
         </is>
       </c>
-      <c r="B436" s="9" t="inlineStr">
+      <c r="B436" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19541,7 +19541,7 @@
           <t>sprinter camper conversion</t>
         </is>
       </c>
-      <c r="B437" s="9" t="inlineStr">
+      <c r="B437" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19574,7 +19574,7 @@
           <t>how much is a sprinter</t>
         </is>
       </c>
-      <c r="B438" s="9" t="inlineStr">
+      <c r="B438" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19607,7 +19607,7 @@
           <t>mercedes benz 12 passenger van</t>
         </is>
       </c>
-      <c r="B439" s="9" t="inlineStr">
+      <c r="B439" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19772,7 +19772,7 @@
           <t>ford e350 camper van</t>
         </is>
       </c>
-      <c r="B444" s="9" t="inlineStr">
+      <c r="B444" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19805,7 +19805,7 @@
           <t>transit 150 ford</t>
         </is>
       </c>
-      <c r="B445" s="9" t="inlineStr">
+      <c r="B445" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19838,7 +19838,7 @@
           <t>transit van conversion</t>
         </is>
       </c>
-      <c r="B446" s="9" t="inlineStr">
+      <c r="B446" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19871,7 +19871,7 @@
           <t>ford transit recreational vehicle</t>
         </is>
       </c>
-      <c r="B447" s="9" t="inlineStr">
+      <c r="B447" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19904,7 +19904,7 @@
           <t>ford transit connect camper conversion</t>
         </is>
       </c>
-      <c r="B448" s="9" t="inlineStr">
+      <c r="B448" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19937,7 +19937,7 @@
           <t>transit connect camper</t>
         </is>
       </c>
-      <c r="B449" s="9" t="inlineStr">
+      <c r="B449" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19970,7 +19970,7 @@
           <t>ford little van</t>
         </is>
       </c>
-      <c r="B450" s="9" t="inlineStr">
+      <c r="B450" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -19988,7 +19988,7 @@
       <c r="E450" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="F450" s="7" t="n">
+      <c r="F450" s="6" t="n">
         <v>42</v>
       </c>
       <c r="G450" t="inlineStr">
@@ -20003,7 +20003,7 @@
           <t>ford transit connect awd</t>
         </is>
       </c>
-      <c r="B451" s="9" t="inlineStr">
+      <c r="B451" s="8" t="inlineStr">
         <is>
           <t>Platforms &amp; Buying</t>
         </is>
@@ -20021,7 +20021,7 @@
       <c r="E451" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="F451" s="7" t="n">
+      <c r="F451" s="6" t="n">
         <v>40</v>
       </c>
       <c r="G451" t="inlineStr">
@@ -20087,7 +20087,7 @@
       <c r="B2" s="3" t="n">
         <v>27100</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -20110,7 +20110,7 @@
       <c r="B3" s="3" t="n">
         <v>27100</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="6" t="n">
         <v>34</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -20133,7 +20133,7 @@
       <c r="B4" s="3" t="n">
         <v>22200</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="9" t="n">
         <v>75</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -20156,7 +20156,7 @@
       <c r="B5" s="3" t="n">
         <v>18100</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="9" t="n">
         <v>74</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -20179,7 +20179,7 @@
       <c r="B6" s="3" t="n">
         <v>18100</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -20202,7 +20202,7 @@
       <c r="B7" s="3" t="n">
         <v>14800</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="9" t="n">
         <v>66</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -20225,7 +20225,7 @@
       <c r="B8" s="3" t="n">
         <v>14800</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="9" t="n">
         <v>74</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -20248,7 +20248,7 @@
       <c r="B9" s="3" t="n">
         <v>14800</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="6" t="n">
         <v>45</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -20294,7 +20294,7 @@
       <c r="B11" s="3" t="n">
         <v>12100</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -20317,7 +20317,7 @@
       <c r="B12" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="9" t="n">
         <v>93</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -20340,7 +20340,7 @@
       <c r="B13" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="9" t="n">
         <v>52</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -20386,7 +20386,7 @@
       <c r="B15" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="9" t="n">
         <v>62</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -20409,7 +20409,7 @@
       <c r="B16" s="3" t="n">
         <v>8100</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -20432,7 +20432,7 @@
       <c r="B17" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -20455,7 +20455,7 @@
       <c r="B18" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -20478,7 +20478,7 @@
       <c r="B19" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="6" t="n">
         <v>46</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -20501,7 +20501,7 @@
       <c r="B20" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>39</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -20524,7 +20524,7 @@
       <c r="B21" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="9" t="n">
         <v>50</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -20547,7 +20547,7 @@
       <c r="B22" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="9" t="n">
         <v>66</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -20570,7 +20570,7 @@
       <c r="B23" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -20593,7 +20593,7 @@
       <c r="B24" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>42</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -20639,7 +20639,7 @@
       <c r="B26" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -20754,7 +20754,7 @@
       <c r="B31" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="6" t="n">
         <v>43</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -20777,7 +20777,7 @@
       <c r="B32" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="6" t="n">
         <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -20800,7 +20800,7 @@
       <c r="B33" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="6" t="n">
         <v>42</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -20846,7 +20846,7 @@
       <c r="B35" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C35" s="9" t="n">
         <v>69</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -20869,7 +20869,7 @@
       <c r="B36" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="9" t="n">
         <v>68</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -20892,7 +20892,7 @@
       <c r="B37" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C37" s="9" t="n">
         <v>81</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -20938,7 +20938,7 @@
       <c r="B39" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -20984,7 +20984,7 @@
       <c r="B41" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="6" t="n">
         <v>35</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -21007,7 +21007,7 @@
       <c r="B42" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="6" t="n">
         <v>34</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -21030,7 +21030,7 @@
       <c r="B43" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -21053,7 +21053,7 @@
       <c r="B44" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="6" t="n">
         <v>43</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -21076,7 +21076,7 @@
       <c r="B45" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="6" t="n">
         <v>38</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -21122,7 +21122,7 @@
       <c r="B47" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="6" t="n">
         <v>45</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -21168,7 +21168,7 @@
       <c r="B49" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="6" t="n">
         <v>40</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -21191,7 +21191,7 @@
       <c r="B50" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -21237,7 +21237,7 @@
       <c r="B52" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="6" t="n">
         <v>31</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -21260,7 +21260,7 @@
       <c r="B53" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="6" t="n">
         <v>45</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -21283,7 +21283,7 @@
       <c r="B54" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="C54" s="6" t="n">
+      <c r="C54" s="9" t="n">
         <v>55</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -21306,7 +21306,7 @@
       <c r="B55" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="6" t="n">
         <v>40</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -21329,7 +21329,7 @@
       <c r="B56" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="6" t="n">
         <v>40</v>
       </c>
       <c r="D56" t="inlineStr">
